--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92286</v>
+        <v>92291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92291</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129227778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91751</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kärrberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>418146</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6598306</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Inge Hedlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Inge Hedlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92301</v>
+        <v>92308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91758</v>
+        <v>91765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91765</v>
+        <v>91767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91767</v>
+        <v>91776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92324</v>
+        <v>92325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91777</v>
+        <v>91780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92330</v>
+        <v>92334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91782</v>
+        <v>91786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91786</v>
+        <v>91787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129046090</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129045896</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91787</v>
+        <v>91790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129227778</v>
       </c>
       <c r="B4" t="n">
-        <v>91790</v>
+        <v>91818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129046090</v>
+        <v>129045896</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129045896</v>
+        <v>129227778</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärntorpet, Kärntorpet, Vrm</t>
+          <t>Kärrberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>418146</v>
       </c>
       <c r="R3" t="n">
-        <v>6598307</v>
+        <v>6598306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,19 +853,9 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129227778</v>
+        <v>129045318</v>
       </c>
       <c r="B4" t="n">
-        <v>91818</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kärrberget, Vrm</t>
+          <t>Kärntorpet, Kärntorpet, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>418146</v>
       </c>
       <c r="R4" t="n">
-        <v>6598306</v>
+        <v>6598307</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,9 +951,19 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +972,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47986-2025 artfynd.xlsx
+++ b/artfynd/A 47986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129045896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129227778</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129045318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>